--- a/dataset/v2/civil_progress.xlsx
+++ b/dataset/v2/civil_progress.xlsx
@@ -569,12 +569,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Substation</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -592,7 +592,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CIV-EXC-1004</t>
+          <t>CIV-DRA-1014</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cut and fill to formation level, well pad Unit 2</t>
+          <t>Precast drain construction, Unit 1 wellhead periphery</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -615,22 +615,27 @@
           <t>CIV</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>21/Mar/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2100</v>
+        <v>260</v>
       </c>
       <c r="J6" t="n">
-        <v>2100</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CIV-EXC-1005</t>
+          <t>CIV-DRA-1051</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -640,12 +645,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>L6</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Excavate unsuitable material, Unit 1 pad</t>
+          <t>Roadside drain slabs, approach road</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -655,30 +660,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Manifold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>850</v>
+        <v>380</v>
       </c>
       <c r="J7" t="n">
-        <v>850</v>
+        <v>380</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CIV-EXC-1020</t>
+          <t>CIV-EXC-1003</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bulk excavation, Unit 2 wellhead cellar</t>
+          <t>Cut and fill to formation level, well pad Unit 1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -708,25 +708,25 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>20/Mar/2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>31/03/2026</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1600</v>
+        <v>2400</v>
       </c>
       <c r="J8" t="n">
-        <v>1600</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CIV-EXC-1030</t>
+          <t>CIV-EXC-1020</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Excavation for flare pit and burn area, manifold south</t>
+          <t>Bulk excavation, Unit 2 wellhead cellar</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -749,21 +749,21 @@
           <t>CIV</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tank Farm</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>23/Mar/2026</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>28/Mar/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>720</v>
+        <v>1600</v>
       </c>
       <c r="J9" t="n">
-        <v>720</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="10">
@@ -794,7 +794,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -807,7 +817,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CIV-EXC-1049</t>
+          <t>CIV-EXC-1115</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -822,7 +832,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Approach road widening, OIL main gate to site (Ch 0-400)</t>
+          <t>Excavation for foundations V-2101 and WHCP-2101, Unit 2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -832,30 +842,30 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>08/Apr/2026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>400</v>
+        <v>580</v>
       </c>
       <c r="J11" t="n">
-        <v>400</v>
+        <v>580</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CIV-FDN-1103</t>
+          <t>CIV-FDN-1106</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -870,7 +880,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Shuttering and concreting M25, separator foundation V-1101</t>
+          <t>Non-shrink grouting, separator skid base ring V-1101</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -878,32 +888,32 @@
           <t>CIV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Workshop</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>16/May/2026</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>48</v>
+        <v>1.2</v>
       </c>
       <c r="J12" t="n">
-        <v>48</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CIV-FDN-1104</t>
+          <t>CIV-FDN-1108</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>V-1101</t>
+          <t>V-1201</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -913,7 +923,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7-day wet cure, separator foundation V-1101</t>
+          <t>Anchor bolt template survey and setting, V-1201</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -921,36 +931,47 @@
           <t>CIV</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tank Farm</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
-        </is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>16</v>
+      </c>
+      <c r="J13" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CIV-FDN-1110</t>
+          <t>CIV-FDN-1118</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>V-2101</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>L5</t>
+          <t>L6</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Wellhead plinth concreting, WHP-1101 and WHP-1102</t>
+          <t>7-day wet cure, V-2101 foundation</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -960,35 +981,29 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Tank Farm</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>36</v>
-      </c>
-      <c r="J14" t="n">
-        <v>36</v>
+          <t>30/Apr/2026</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CIV-FDN-1117</t>
+          <t>CIV-FDN-1126</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>V-2101</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -998,7 +1013,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Separator foundation, reinforcement and pour, V-2101</t>
+          <t>Flare stack foundation and guy anchor blocks, FST-1301</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1008,35 +1023,35 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Substation</t>
+          <t>Manifold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>17/Apr/2026</t>
+          <t>06/Apr/2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>23/Apr/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="J15" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CIV-FDN-1150</t>
+          <t>CIV-FDN-1127</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TK-2101</t>
+          <t>FST-1301</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1046,7 +1061,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ring wall foundation, storage tank TK-2101</t>
+          <t>Anchor bolts and template, flare stack FST-1301</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1056,35 +1071,35 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Tank Farm</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>10/Apr/2026</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>11/Apr/2026</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>120</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CIV-FDN-1154</t>
+          <t>CIV-FDN-1152</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TK-2102</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1094,7 +1109,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Dyke wall construction, tank farm bund</t>
+          <t>Ring wall foundation, storage tank TK-2102</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1102,32 +1117,37 @@
           <t>CIV</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>30/Apr/2026</t>
+          <t>25/Apr/2026</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>210</v>
+        <v>110</v>
       </c>
       <c r="J17" t="n">
-        <v>210</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CIV-FDN-1162</t>
+          <t>CIV-FDN-1153</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OWS-2201</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1137,7 +1157,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Transformer plinths and cable trenches, T-1 and T-2</t>
+          <t>Oil-water separator pit civil works, OWS-2201</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1147,30 +1167,30 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>11/May/2026</t>
+          <t>13/Apr/2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CIV-FDN-1165</t>
+          <t>CIV-FDN-1154</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1185,7 +1205,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sleeper and column footings, pipe rack Module 1</t>
+          <t>Dyke wall construction, tank farm bund</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1193,32 +1213,27 @@
           <t>CIV</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20/Apr/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>24/Apr/2026</t>
+          <t>30/Apr/2026</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="J19" t="n">
-        <v>90</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CIV-FDN-1166</t>
+          <t>CIV-FDN-1167</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1233,7 +1248,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sleeper and column footings, pipe rack Module 2</t>
+          <t>Sleeper and column footings, pipe rack Module 3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1243,25 +1258,25 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>04/May/2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>07/May/2026</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="J20" t="n">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CIV-FDN-1167</t>
+          <t>CIV-FLR-1021</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1276,7 +1291,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sleeper and column footings, pipe rack Module 3</t>
+          <t>Anti-termite treatment and PCC blinding, Unit 2 pad</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1286,30 +1301,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Tank Farm</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>07/May/2026</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>68</v>
+        <v>950</v>
       </c>
       <c r="J21" t="n">
-        <v>68</v>
+        <v>950</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CIV-FIL-1006</t>
+          <t>CIV-FNC-1052</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1319,12 +1329,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>L6</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Place and compact selected fill, Unit 1 pad</t>
+          <t>Fencing, approach road stretch</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1332,27 +1342,27 @@
           <t>CIV</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Substation</t>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1900</v>
+        <v>420</v>
       </c>
       <c r="J22" t="n">
-        <v>1900</v>
+        <v>420</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CIV-FIL-1007</t>
+          <t>CIV-RDS-1012</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1367,7 +1377,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Proof roll and level survey, Unit 1 pad formation</t>
+          <t>Lay and compact WMM course, road U1 Ch 0-160</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1382,25 +1392,20 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2400</v>
+        <v>160</v>
       </c>
       <c r="J23" t="n">
-        <v>2400</v>
+        <v>160</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CIV-FNC-1032</t>
+          <t>CIV-RDS-1013</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1410,12 +1415,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>L5</t>
+          <t>L6</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Chain-link fencing with posts, site perimeter</t>
+          <t>Lay and compact WMM course, road U1 Ch 160-320</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1425,25 +1430,30 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>22/Apr/2026</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>850</v>
+        <v>160</v>
       </c>
       <c r="J24" t="n">
-        <v>850</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CIV-FNC-1033</t>
+          <t>CIV-RDS-1050</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1458,7 +1468,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Gate installation, main and emergency exits</t>
+          <t>BC course laying, approach road</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1468,30 +1478,30 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Manifold</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>16/Apr/2026</t>
+          <t>23/Mar/2026</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>18/Apr/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>400</v>
       </c>
       <c r="J25" t="n">
-        <v>3</v>
+        <v>400</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CIV-RDS-1010</t>
+          <t>CIV-SRV-1001</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1506,7 +1516,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sub-grade preparation, internal access road Unit 1</t>
+          <t>Topographic survey and grid establishment, well-site boundary</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1514,32 +1524,27 @@
           <t>CIV</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>03/Apr/2026</t>
+          <t>02/Mar/2026</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>07/03/2026</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>320</v>
+        <v>4800</v>
       </c>
       <c r="J26" t="n">
-        <v>320</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CIV-RDS-1013</t>
+          <t>CIV-UGS-1181</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1549,12 +1554,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>L6</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Lay and compact WMM course, road U1 Ch 160-320</t>
+          <t>Cable trench with precast covers, Unit 2 to substation</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1569,25 +1574,25 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>18/Apr/2026</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="J27" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CIV-SRV-1001</t>
+          <t>CIV-UGS-1182</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1602,7 +1607,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Topographic survey and grid establishment, well-site boundary</t>
+          <t>Trench sand bedding and protection tiles, cable routes</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1612,30 +1617,30 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Substation</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>07/03/2026</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4800</v>
+        <v>400</v>
       </c>
       <c r="J28" t="n">
-        <v>4800</v>
+        <v>400</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CIV-SRV-1002</t>
+          <t>CIV-YRD-1046</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1650,7 +1655,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Clearing and grubbing, well pad and approach road</t>
+          <t>Crusher fines laying, equipment laydown yard</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1665,19 +1670,19 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>27/Mar/2026</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>6200</v>
+        <v>1200</v>
       </c>
       <c r="J29" t="n">
-        <v>6200</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="30">
@@ -1708,17 +1713,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Substation</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
+          <t>Tank Farm</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>12/Mar/2026</t>
+          <t>2026-03-12</t>
         </is>
       </c>
     </row>
